--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -830,10 +830,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E4" s="9">
-        <v>9397</v>
+        <v>11300</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -899,10 +899,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E7" s="9">
-        <v>9397</v>
+        <v>11243</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -922,10 +922,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E8" s="9">
-        <v>9397</v>
+        <v>11251</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>2016-2025</t>
+  </si>
+  <si>
+    <t>2021-2025</t>
   </si>
 </sst>
 </file>
@@ -853,10 +856,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E5" s="9">
-        <v>8605</v>
+        <v>6382</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -879,10 +879,10 @@
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E6" s="9">
-        <v>6456</v>
+        <v>6600</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1362,10 +1362,10 @@
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E6" s="9">
-        <v>376</v>
+        <v>470</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>62</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Число организаций, использовавших ИИ</t>
-  </si>
-  <si>
-    <t>2021-2024</t>
   </si>
   <si>
     <t>1_ОКВЭД.xlsx</t>
@@ -813,7 +810,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -824,16 +821,16 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="9">
         <v>11300</v>
@@ -842,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -856,7 +853,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" s="9">
         <v>6382</v>
@@ -865,21 +862,21 @@
         <v>10</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="9">
         <v>6600</v>
@@ -888,21 +885,21 @@
         <v>10</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="9">
         <v>11243</v>
@@ -911,21 +908,21 @@
         <v>10</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="9">
         <v>11251</v>
@@ -934,7 +931,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -962,7 +959,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1019,7 +1016,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1039,7 +1036,7 @@
         <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="4">
         <v>4084</v>
@@ -1062,7 +1059,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="4">
         <v>9211</v>
@@ -1085,7 +1082,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="4">
         <v>1915</v>
@@ -1108,7 +1105,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="4">
         <v>4260</v>
@@ -1191,7 +1188,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1202,16 +1199,16 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="20">
         <v>1207</v>
@@ -1220,15 +1217,15 @@
         <v>10</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>23</v>
@@ -1243,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1265,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1296,7 +1293,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1307,10 +1304,10 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -1322,15 +1319,15 @@
         <v>752</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>40</v>
@@ -1339,47 +1336,47 @@
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="E5" s="9">
-        <v>376</v>
+        <v>470</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="9">
         <v>470</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
@@ -1391,18 +1388,18 @@
         <v>752</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
@@ -1414,15 +1411,15 @@
         <v>752</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -1437,15 +1434,15 @@
         <v>658</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1456,7 +1453,7 @@
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>11</v>
@@ -1471,15 +1468,15 @@
         <v>658</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>15</v>
@@ -1494,15 +1491,15 @@
         <v>846</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1513,7 +1510,7 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>22</v>
@@ -1522,21 +1519,21 @@
         <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="4">
         <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>26</v>
@@ -1545,21 +1542,21 @@
         <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="4">
         <v>940</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>28</v>
@@ -1568,21 +1565,21 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="4">
         <v>526</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>31</v>
@@ -1591,21 +1588,21 @@
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="4">
         <v>939</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>33</v>
@@ -1620,15 +1617,15 @@
         <v>846</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>37</v>
@@ -1643,15 +1640,15 @@
         <v>846</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>38</v>
@@ -1666,15 +1663,15 @@
         <v>846</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>23</v>
@@ -1700,18 +1697,18 @@
         <v>752</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>75</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>76</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>23</v>
@@ -1723,10 +1720,10 @@
         <v>846</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1313,10 +1313,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E4" s="9">
-        <v>752</v>
+        <v>846</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>61</v>
@@ -1382,10 +1382,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E7" s="9">
-        <v>752</v>
+        <v>846</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>61</v>
@@ -1405,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E8" s="9">
-        <v>752</v>
+        <v>846</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>61</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1128,10 +1128,10 @@
         <v>23</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E18" s="4">
-        <v>1660</v>
+        <v>1297</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1151,10 +1151,10 @@
         <v>23</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E19" s="4">
-        <v>1658</v>
+        <v>1287</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1174,10 +1174,10 @@
         <v>23</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E20" s="4">
-        <v>1656</v>
+        <v>753</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1611,10 +1611,10 @@
         <v>23</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E18" s="4">
-        <v>846</v>
+        <v>922</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>61</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1634,10 +1634,10 @@
         <v>23</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E19" s="4">
-        <v>846</v>
+        <v>922</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>61</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -1657,10 +1657,10 @@
         <v>23</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E20" s="4">
-        <v>846</v>
+        <v>829</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>61</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>2021-2025</t>
+  </si>
+  <si>
+    <t>2018-2025</t>
   </si>
 </sst>
 </file>
@@ -979,10 +982,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="E11" s="14">
-        <v>1567</v>
+        <v>1345</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -948,10 +948,10 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="E9" s="16">
-        <v>1567</v>
+        <v>2135</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>10</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1431,10 +1431,10 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="E9" s="16">
-        <v>658</v>
+        <v>752</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>61</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>ед.</t>
-  </si>
-  <si>
-    <t>2018-2024</t>
   </si>
   <si>
     <t xml:space="preserve">Структура </t>
@@ -785,7 +782,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -805,15 +802,15 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -824,117 +821,117 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="9">
         <v>11300</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="9">
         <v>6382</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" s="9">
         <v>6600</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="9">
         <v>11243</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="9">
         <v>11251</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -948,21 +945,21 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E9" s="16">
         <v>2135</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -973,53 +970,53 @@
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>13</v>
-      </c>
       <c r="D11" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" s="14">
         <v>1345</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="E12" s="14">
         <v>1707</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1030,168 +1027,168 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="4">
         <v>4084</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="4">
         <v>9211</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" s="4">
         <v>1915</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17" s="4">
         <v>4260</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="4">
         <v>1297</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="4">
         <v>1287</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="4">
         <v>753</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1202,48 +1199,48 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="C22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>56</v>
       </c>
       <c r="E22" s="20">
         <v>1207</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>58</v>
-      </c>
       <c r="C23" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="20">
         <v>513</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1265,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,15 +1285,15 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1307,122 +1304,122 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" s="9">
         <v>846</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="9">
         <v>470</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" s="9">
         <v>470</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E7" s="9">
         <v>846</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" s="9">
         <v>846</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -1431,21 +1428,21 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E9" s="16">
         <v>752</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1456,53 +1453,53 @@
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="E11" s="14">
-        <v>658</v>
+        <v>742</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="14">
         <v>846</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1513,168 +1510,168 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="4">
         <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" s="4">
         <v>940</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" s="4">
         <v>526</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17" s="4">
         <v>939</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="4">
         <v>922</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19" s="4">
         <v>922</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="4">
         <v>829</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1685,48 +1682,48 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" s="20">
         <v>752</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>75</v>
-      </c>
       <c r="C23" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="20">
         <v>846</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1002,10 +1002,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E12" s="14">
-        <v>1707</v>
+        <v>1391</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>9</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1485,10 +1485,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="E12" s="14">
-        <v>846</v>
+        <v>924</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>60</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -1231,10 +1231,10 @@
         <v>22</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="E23" s="20">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>9</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -70,9 +70,6 @@
     <t>researchers_s</t>
   </si>
   <si>
-    <t>2017-2024</t>
-  </si>
-  <si>
     <t>11_ОКВЭД2_публ.xlsx</t>
   </si>
   <si>
@@ -247,33 +244,6 @@
     <t>Валовая добавленная стоимость по регионам РФ</t>
   </si>
   <si>
-    <r>
-      <t>Объем отгруженных товаров собственного производства, выполненных работ и услуг собственными силами (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>СУММА</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>factoriescap_r</t>
   </si>
   <si>
@@ -320,6 +290,9 @@
   </si>
   <si>
     <t>2018-2025</t>
+  </si>
+  <si>
+    <t>Объем отгруженных товаров собственного производства, выполненных работ и услуг собственными силами</t>
   </si>
 </sst>
 </file>
@@ -805,12 +778,12 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -821,16 +794,16 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="9">
         <v>11300</v>
@@ -839,21 +812,21 @@
         <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>39</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" s="9">
         <v>6382</v>
@@ -862,21 +835,21 @@
         <v>9</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" s="9">
         <v>6600</v>
@@ -885,21 +858,21 @@
         <v>9</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="9">
         <v>11243</v>
@@ -908,21 +881,21 @@
         <v>9</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="9">
         <v>11251</v>
@@ -931,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -945,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="16">
         <v>2135</v>
@@ -954,12 +927,12 @@
         <v>9</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -979,7 +952,7 @@
         <v>12</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E11" s="14">
         <v>1345</v>
@@ -988,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1002,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="14">
         <v>1391</v>
@@ -1011,12 +984,12 @@
         <v>9</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1027,16 +1000,16 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="4">
         <v>4084</v>
@@ -1045,21 +1018,21 @@
         <v>9</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E15" s="4">
         <v>9211</v>
@@ -1068,21 +1041,21 @@
         <v>9</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16" s="4">
         <v>1915</v>
@@ -1091,21 +1064,21 @@
         <v>9</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" s="4">
         <v>4260</v>
@@ -1114,21 +1087,21 @@
         <v>9</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" s="4">
         <v>1297</v>
@@ -1137,21 +1110,21 @@
         <v>9</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" s="4">
         <v>1287</v>
@@ -1160,21 +1133,21 @@
         <v>9</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" s="4">
         <v>753</v>
@@ -1183,12 +1156,12 @@
         <v>9</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1199,16 +1172,16 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="C22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>55</v>
       </c>
       <c r="E22" s="20">
         <v>1207</v>
@@ -1217,21 +1190,21 @@
         <v>9</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E23" s="20">
         <v>570</v>
@@ -1240,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1265,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,12 +1261,12 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1304,122 +1277,122 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="9">
         <v>846</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" s="9">
         <v>470</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" s="9">
         <v>470</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" s="9">
         <v>846</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E8" s="9">
         <v>846</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -1428,21 +1401,21 @@
         <v>7</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="16">
         <v>752</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1453,7 +1426,7 @@
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>10</v>
@@ -1462,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E11" s="14">
         <v>742</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>14</v>
@@ -1485,21 +1458,21 @@
         <v>12</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" s="14">
         <v>924</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1510,168 +1483,168 @@
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="4">
         <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E15" s="4">
         <v>940</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16" s="4">
         <v>526</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" s="4">
         <v>939</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E18" s="4">
         <v>922</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E19" s="4">
         <v>922</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E20" s="4">
         <v>829</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1682,48 +1655,48 @@
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E22" s="20">
-        <v>752</v>
+        <v>846</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>74</v>
-      </c>
       <c r="C23" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="20">
         <v>846</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="По отраслям" sheetId="1" r:id="rId1"/>
-    <sheet name="По регионам" sheetId="2" r:id="rId2"/>
+    <sheet name="По отраслям RU" sheetId="1" r:id="rId1"/>
+    <sheet name="По регионам RU" sheetId="2" r:id="rId2"/>
+    <sheet name="По регионам KZ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="99">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -293,6 +294,30 @@
   </si>
   <si>
     <t>Объем отгруженных товаров собственного производства, выполненных работ и услуг собственными силами</t>
+  </si>
+  <si>
+    <t>VDS_r.kz</t>
+  </si>
+  <si>
+    <t>Признаки по регионам Казахстана (приставка _r - region, .kz - Казахстан)</t>
+  </si>
+  <si>
+    <t>Валовая добавленная стоимость малого и среднего предпринимательства по регионам</t>
+  </si>
+  <si>
+    <t>млн. тенге</t>
+  </si>
+  <si>
+    <t>2005-2024</t>
+  </si>
+  <si>
+    <t>region, year, value</t>
+  </si>
+  <si>
+    <t>Исходник-форма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики (отраслевая статистика, статистика предприятий) </t>
   </si>
 </sst>
 </file>
@@ -372,7 +397,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -395,11 +420,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -460,6 +511,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1703,4 +1763,88 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
+    <col min="7" max="7" width="38.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="20">
+        <v>356</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="102">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -318,6 +318,15 @@
   </si>
   <si>
     <t xml:space="preserve">Бюро национальной статистики (отраслевая статистика, статистика предприятий) </t>
+  </si>
+  <si>
+    <t>Innovcosts_r.kz</t>
+  </si>
+  <si>
+    <t>Затраты на инновации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики (Об инновационной деятельности предприятий в Республике Казахстан) </t>
   </si>
 </sst>
 </file>
@@ -450,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,13 +521,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1767,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1808,10 +1820,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="26"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -1822,7 +1832,7 @@
       <c r="A4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -1839,6 +1849,29 @@
       </c>
       <c r="G4" s="21" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="4">
+        <v>102</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="106">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t xml:space="preserve">Бюро национальной статистики (Об инновационной деятельности предприятий в Республике Казахстан) </t>
+  </si>
+  <si>
+    <t>inetusage_r.kz</t>
+  </si>
+  <si>
+    <t>Количество организаций, использующих сеть Интернет</t>
+  </si>
+  <si>
+    <t>2004-2025</t>
+  </si>
+  <si>
+    <t>Бюро национальной статистики (информационно-коммуникационные технологии)</t>
   </si>
 </sst>
 </file>
@@ -459,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -524,13 +536,16 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1779,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1820,8 +1835,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -1855,7 +1870,7 @@
       <c r="A5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="26" t="s">
         <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1872,6 +1887,29 @@
       </c>
       <c r="G5" s="6" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="29">
+        <v>406</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -339,6 +339,15 @@
   </si>
   <si>
     <t>Бюро национальной статистики (информационно-коммуникационные технологии)</t>
+  </si>
+  <si>
+    <t>Количество компьютеров в организациях</t>
+  </si>
+  <si>
+    <t>region,  year, value</t>
+  </si>
+  <si>
+    <t>PCusage_r.kz</t>
   </si>
 </sst>
 </file>
@@ -539,14 +548,14 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1794,7 +1803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1835,8 +1844,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -1890,25 +1899,48 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="9">
+        <v>406</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C7" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D7" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E7" s="27">
         <v>406</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F7" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G7" s="27" t="s">
         <v>105</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="115">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -317,18 +317,9 @@
     <t>Исходник-форма</t>
   </si>
   <si>
-    <t xml:space="preserve">Бюро национальной статистики (отраслевая статистика, статистика предприятий) </t>
-  </si>
-  <si>
     <t>Innovcosts_r.kz</t>
   </si>
   <si>
-    <t>Затраты на инновации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бюро национальной статистики (Об инновационной деятельности предприятий в Республике Казахстан) </t>
-  </si>
-  <si>
     <t>inetusage_r.kz</t>
   </si>
   <si>
@@ -338,9 +329,6 @@
     <t>2004-2025</t>
   </si>
   <si>
-    <t>Бюро национальной статистики (информационно-коммуникационные технологии)</t>
-  </si>
-  <si>
     <t>Количество компьютеров в организациях</t>
   </si>
   <si>
@@ -348,13 +336,56 @@
   </si>
   <si>
     <t>PCusage_r.kz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (отраслевая статистика, статистика предприятий) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (Об инновационной деятельности предприятий в Республике Казахстан) </t>
+  </si>
+  <si>
+    <t>Бюро национальной статистики Казахстана (информационно-коммуникационные технологии)</t>
+  </si>
+  <si>
+    <t>ITcosts_r.kz</t>
+  </si>
+  <si>
+    <t>2007-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (Статистика регионов, Динамические ряды) </t>
+  </si>
+  <si>
+    <t>Общие затраты на информационно-коммуникационные технологии (ИКТ)</t>
+  </si>
+  <si>
+    <t>Затраты на обучение сотрудников, связанные с развитием и использованием ИКТ</t>
+  </si>
+  <si>
+    <r>
+      <t>Затраты на инновации</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (! не входит в состав ИКТ !)</t>
+    </r>
+  </si>
+  <si>
+    <t>trainingcosts_r.kz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +414,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -1803,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1872,76 +1911,122 @@
         <v>96</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="E5" s="4">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="4">
+        <v>193</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="4">
+        <v>102</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="E8" s="9">
+        <v>406</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D9" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="27">
         <v>406</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F9" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>107</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="27">
-        <v>406</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1949,5 +2034,6 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="119">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -379,6 +379,18 @@
   </si>
   <si>
     <t>trainingcosts_r.kz</t>
+  </si>
+  <si>
+    <t>RDcosts_r.kz</t>
+  </si>
+  <si>
+    <t>Внутренние затраты на НИОКР по областям</t>
+  </si>
+  <si>
+    <t>2000-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (Статистика образования, науки и инноваций) </t>
   </si>
 </sst>
 </file>
@@ -1842,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1960,72 +1972,95 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="E7" s="4">
-        <v>102</v>
+        <v>491</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="4">
+        <v>102</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E9" s="9">
         <v>406</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G9" s="27" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B10" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E10" s="27">
         <v>406</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F10" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G10" s="27" t="s">
         <v>107</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -391,6 +391,12 @@
   </si>
   <si>
     <t xml:space="preserve">Бюро национальной статистики Казахстана (Статистика образования, науки и инноваций) </t>
+  </si>
+  <si>
+    <t>researchers_r.kz</t>
+  </si>
+  <si>
+    <t>Численность работников, осуществлявших НИОКР</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -2019,48 +2025,71 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="14">
+        <v>490</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B10" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E10" s="9">
         <v>406</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G10" s="27" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B11" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D11" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E11" s="27">
         <v>406</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F11" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G11" s="27" t="s">
         <v>107</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="123">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>Численность работников, осуществлявших НИОКР</t>
+  </si>
+  <si>
+    <t>researchorg_r.kz</t>
+  </si>
+  <si>
+    <t>Количество предприятий осуществлявших НИОКР</t>
   </si>
 </sst>
 </file>
@@ -537,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -613,6 +619,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1860,7 +1869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -2048,48 +2057,71 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="16">
+        <v>492</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B11" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E11" s="9">
         <v>406</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G11" s="27" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D12" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E12" s="27">
         <v>406</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F12" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G12" s="27" t="s">
         <v>107</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="126">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -403,6 +403,15 @@
   </si>
   <si>
     <t>Количество предприятий осуществлявших НИОКР</t>
+  </si>
+  <si>
+    <t>ITusage_r.kz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество отчитавшихся предприятий, использовавших цифровые технологии, всего </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (Информационно-коммуникационные технологии и связи) </t>
   </si>
 </sst>
 </file>
@@ -543,7 +552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -596,9 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -614,14 +620,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1427,10 +1439,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1568,10 +1580,10 @@
       <c r="E9" s="16">
         <v>752</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="23" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1590,7 +1602,7 @@
       <c r="A11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1862,6 +1874,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1869,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1922,7 +1937,7 @@
       <c r="A4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -1945,7 +1960,7 @@
       <c r="A5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>111</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1968,7 +1983,7 @@
       <c r="A6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1991,7 +2006,7 @@
       <c r="A7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>116</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2014,7 +2029,7 @@
       <c r="A8" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2037,7 +2052,7 @@
       <c r="A9" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>120</v>
       </c>
       <c r="C9" s="14" t="s">
@@ -2052,7 +2067,7 @@
       <c r="F9" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="22" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2072,56 +2087,79 @@
       <c r="E10" s="16">
         <v>492</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="27" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="9">
+        <v>102</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E14" s="9">
         <v>406</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G14" s="26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C15" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D15" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E15" s="26">
         <v>406</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F15" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G15" s="26" t="s">
         <v>107</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="128">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -412,6 +412,12 @@
   </si>
   <si>
     <t xml:space="preserve">Бюро национальной статистики Казахстана (Информационно-коммуникационные технологии и связи) </t>
+  </si>
+  <si>
+    <t>BDusage_r.kz</t>
+  </si>
+  <si>
+    <t>Количество отчитавшихся предприятий, проводивших анализ больших данных</t>
   </si>
 </sst>
 </file>
@@ -623,17 +629,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1439,10 +1445,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1925,8 +1931,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -2114,6 +2120,29 @@
         <v>96</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="9">
+        <v>102</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>125</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="130">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -418,6 +418,12 @@
   </si>
   <si>
     <t>Количество отчитавшихся предприятий, проводивших анализ больших данных</t>
+  </si>
+  <si>
+    <t>AIusage_r.kz</t>
+  </si>
+  <si>
+    <t>Количество организаций, использующих технологии искусственного интеллекта</t>
   </si>
 </sst>
 </file>
@@ -635,11 +641,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1890,7 +1896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1931,271 +1937,326 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
+      <c r="A3" s="30" t="s">
+        <v>42</v>
+      </c>
       <c r="B3" s="31"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-    </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="9">
+        <v>102</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="9">
+        <v>102</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="9">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="9">
+        <v>406</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="26">
+        <v>406</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="14">
+        <v>490</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="16">
+        <v>492</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="4">
+        <v>206</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="4">
+        <v>193</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="4">
+        <v>491</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="4">
+        <v>102</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B18" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C18" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D18" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E18" s="20">
         <v>356</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F18" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G18" s="21" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="4">
-        <v>206</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="4">
-        <v>193</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="4">
-        <v>491</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="4">
-        <v>102</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="14">
-        <v>490</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="16">
-        <v>492</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="9">
-        <v>102</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="9">
-        <v>102</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="9">
-        <v>406</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="26">
-        <v>406</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:B3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="По отраслям RU" sheetId="1" r:id="rId1"/>
     <sheet name="По регионам RU" sheetId="2" r:id="rId2"/>
-    <sheet name="По регионам KZ" sheetId="3" r:id="rId3"/>
+    <sheet name="По отраслям KZ" sheetId="4" r:id="rId3"/>
+    <sheet name="По регионам KZ" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="136">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -424,6 +425,24 @@
   </si>
   <si>
     <t>Количество организаций, использующих технологии искусственного интеллекта</t>
+  </si>
+  <si>
+    <t>ITusage_s.kz</t>
+  </si>
+  <si>
+    <t>BDusage_s.kz</t>
+  </si>
+  <si>
+    <t>AIusage_s.kz</t>
+  </si>
+  <si>
+    <t>PCusage_s.kz</t>
+  </si>
+  <si>
+    <t>inetusage_s.kz</t>
+  </si>
+  <si>
+    <t>Признаки по регионам Казахстана (приставка _s - sector, .kz - Казахстан)</t>
   </si>
 </sst>
 </file>
@@ -636,16 +655,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -931,8 +950,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
+    <col min="2" max="2" width="57.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" customWidth="1"/>
@@ -1413,12 +1432,12 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="57.28515625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
     <col min="7" max="7" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1451,10 +1470,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="29"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1895,6 +1914,171 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39.85546875" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="43.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="9">
+        <v>119</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="26">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1937,10 +2121,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="138">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -443,6 +443,12 @@
   </si>
   <si>
     <t>Признаки по регионам Казахстана (приставка _s - sector, .kz - Казахстан)</t>
+  </si>
+  <si>
+    <t>sector, year, value</t>
+  </si>
+  <si>
+    <t>Количество организаций, использующих компьютеры</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1003,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>45</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>37</v>
       </c>
@@ -1043,7 +1049,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>40</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>47</v>
       </c>
@@ -1089,7 +1095,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>49</v>
       </c>
@@ -1112,7 +1118,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1152,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>11</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1203,7 +1209,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
@@ -1226,7 +1232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1295,7 +1301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
@@ -1318,7 +1324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
@@ -1341,7 +1347,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
@@ -1375,7 +1381,7 @@
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>52</v>
       </c>
@@ -1480,7 +1486,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>63</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>61</v>
       </c>
@@ -1526,7 +1532,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
@@ -1549,7 +1555,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>65</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>66</v>
       </c>
@@ -1595,7 +1601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>76</v>
       </c>
@@ -1629,7 +1635,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>77</v>
       </c>
@@ -1652,7 +1658,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>78</v>
       </c>
@@ -1686,7 +1692,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
@@ -1709,7 +1715,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>68</v>
       </c>
@@ -1732,7 +1738,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>69</v>
       </c>
@@ -1755,7 +1761,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>70</v>
       </c>
@@ -1778,7 +1784,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>80</v>
       </c>
@@ -1801,7 +1807,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>81</v>
       </c>
@@ -1824,7 +1830,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>82</v>
       </c>
@@ -1858,7 +1864,7 @@
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>74</v>
       </c>
@@ -1881,7 +1887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>72</v>
       </c>
@@ -1983,7 +1989,7 @@
         <v>119</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>125</v>
@@ -2004,7 +2010,7 @@
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>125</v>
@@ -2024,8 +2030,8 @@
         <v>2025</v>
       </c>
       <c r="E6" s="26"/>
-      <c r="F6" s="26" t="s">
-        <v>96</v>
+      <c r="F6" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>125</v>
@@ -2036,7 +2042,7 @@
         <v>133</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>7</v>
@@ -2044,9 +2050,11 @@
       <c r="D7" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26" t="s">
-        <v>103</v>
+      <c r="E7" s="26">
+        <v>119</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>107</v>
@@ -2066,8 +2074,8 @@
         <v>88</v>
       </c>
       <c r="E8" s="26"/>
-      <c r="F8" s="26" t="s">
-        <v>96</v>
+      <c r="F8" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>107</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -2008,7 +2008,9 @@
       <c r="D5" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="9">
+        <v>108</v>
+      </c>
       <c r="F5" s="9" t="s">
         <v>136</v>
       </c>
@@ -2073,7 +2075,9 @@
       <c r="D8" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="26">
+        <v>119</v>
+      </c>
       <c r="F8" s="9" t="s">
         <v>136</v>
       </c>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -2031,7 +2031,9 @@
       <c r="D6" s="26">
         <v>2025</v>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="26">
+        <v>21</v>
+      </c>
       <c r="F6" s="9" t="s">
         <v>136</v>
       </c>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="139">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -450,12 +450,15 @@
   <si>
     <t>Количество организаций, использующих компьютеры</t>
   </si>
+  <si>
+    <t>ITcosts_s.kz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,6 +498,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -589,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -671,6 +680,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1921,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
@@ -2087,8 +2099,43 @@
         <v>107</v>
       </c>
     </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="4">
+        <v>119</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="142">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -452,6 +452,15 @@
   </si>
   <si>
     <t>ITcosts_s.kz</t>
+  </si>
+  <si>
+    <t>2010-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (Национальные счета) </t>
+  </si>
+  <si>
+    <t>VDS_s.kz</t>
   </si>
 </sst>
 </file>
@@ -675,14 +684,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1488,10 +1497,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1933,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
@@ -2129,8 +2138,42 @@
       <c r="F10" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="30" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="20">
+        <v>284</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям RU" sheetId="1" r:id="rId1"/>
@@ -303,9 +303,6 @@
     <t>Признаки по регионам Казахстана (приставка _r - region, .kz - Казахстан)</t>
   </si>
   <si>
-    <t>Валовая добавленная стоимость малого и среднего предпринимательства по регионам</t>
-  </si>
-  <si>
     <t>млн. тенге</t>
   </si>
   <si>
@@ -461,6 +458,22 @@
   </si>
   <si>
     <t>VDS_s.kz</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Валовая добавленная стоимость малого и среднего предпринимательства по регионам </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(ИСПРАВИТЬ)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -516,7 +529,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +563,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -692,6 +711,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,7 +1026,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="57.42578125" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" customWidth="1"/>
@@ -1025,400 +1074,400 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="26" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="26">
         <v>11300</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="26" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>6382</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>6600</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>11243</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="26" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="26" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="26">
         <v>11251</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="34">
         <v>2135</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="22">
         <v>1345</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="22" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="22">
         <v>1391</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="6">
         <v>4084</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="6">
         <v>9211</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="6">
         <v>1915</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="6">
         <v>4260</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="6">
         <v>1297</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="6">
         <v>1287</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="6">
         <v>753</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <v>1207</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="21" t="s">
         <v>9</v>
       </c>
       <c r="G22" s="21" t="s">
@@ -1426,22 +1475,22 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>55</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="21">
         <v>570</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="21" t="s">
         <v>9</v>
       </c>
       <c r="G23" s="21" t="s">
@@ -1460,7 +1509,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="48.85546875" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
@@ -1508,423 +1557,423 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="26">
         <v>846</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="26" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>470</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="26" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>470</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="26" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>846</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="26" t="s">
         <v>66</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="26">
         <v>846</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="26" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
         <v>76</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="34">
         <v>752</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="27" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>77</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="22">
         <v>742</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>78</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="22">
         <v>924</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="6">
         <v>188</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="6">
         <v>940</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="6">
         <v>526</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="6">
         <v>939</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="6">
         <v>922</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="6">
         <v>922</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="6">
         <v>829</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <v>846</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="21" t="s">
         <v>59</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="21">
         <v>846</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="21" t="s">
         <v>59</v>
       </c>
       <c r="G23" s="21" t="s">
@@ -1956,7 +2005,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1979,7 +2028,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1995,10 +2044,10 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -2010,18 +2059,18 @@
         <v>119</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
@@ -2033,18 +2082,18 @@
         <v>108</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>7</v>
@@ -2056,18 +2105,18 @@
         <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>7</v>
@@ -2079,18 +2128,18 @@
         <v>119</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>7</v>
@@ -2102,10 +2151,10 @@
         <v>119</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2121,13 +2170,13 @@
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>88</v>
@@ -2136,10 +2185,10 @@
         <v>119</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2155,25 +2204,25 @@
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>94</v>
-      </c>
       <c r="D12" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E12" s="20">
         <v>284</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2221,7 +2270,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2237,10 +2286,10 @@
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -2252,18 +2301,18 @@
         <v>102</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
@@ -2275,18 +2324,18 @@
         <v>102</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
@@ -2298,56 +2347,56 @@
         <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E7" s="9">
         <v>406</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E8" s="26">
         <v>406</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,48 +2412,48 @@
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>119</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>120</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E10" s="14">
         <v>490</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>121</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>122</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E11" s="16">
         <v>492</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2420,82 +2469,82 @@
     </row>
     <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="E13" s="4">
         <v>206</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" s="4">
         <v>193</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="E15" s="4">
         <v>491</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>88</v>
@@ -2504,10 +2553,10 @@
         <v>102</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2522,26 +2571,26 @@
       <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="E18" s="41">
+        <v>356</v>
+      </c>
+      <c r="F18" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="20">
-        <v>356</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>105</v>
+      <c r="G18" s="42" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="140">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -306,9 +306,6 @@
     <t>млн. тенге</t>
   </si>
   <si>
-    <t>2005-2024</t>
-  </si>
-  <si>
     <t>region, year, value</t>
   </si>
   <si>
@@ -334,9 +331,6 @@
   </si>
   <si>
     <t>PCusage_r.kz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бюро национальной статистики Казахстана (отраслевая статистика, статистика предприятий) </t>
   </si>
   <si>
     <t xml:space="preserve">Бюро национальной статистики Казахстана (Об инновационной деятельности предприятий в Республике Казахстан) </t>
@@ -460,20 +454,7 @@
     <t>VDS_s.kz</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Валовая добавленная стоимость малого и среднего предпринимательства по регионам </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(ИСПРАВИТЬ)</t>
-    </r>
+    <t xml:space="preserve">Валовая добавленная стоимость по регионам </t>
   </si>
 </sst>
 </file>
@@ -529,7 +510,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -563,12 +544,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -706,41 +681,32 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1189,38 +1155,38 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="31">
         <v>2135</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="31" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -1269,15 +1235,15 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -1441,15 +1407,15 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
@@ -1546,10 +1512,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1579,7 +1545,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>61</v>
       </c>
@@ -1602,7 +1568,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>62</v>
       </c>
@@ -1625,7 +1591,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>65</v>
       </c>
@@ -1671,20 +1637,20 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
         <v>76</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="31">
         <v>752</v>
       </c>
       <c r="F9" s="27" t="s">
@@ -1695,17 +1661,17 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-    </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>77</v>
       </c>
@@ -1728,7 +1694,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>78</v>
       </c>
@@ -1752,17 +1718,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-    </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>67</v>
       </c>
@@ -1785,7 +1751,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>68</v>
       </c>
@@ -1808,7 +1774,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>69</v>
       </c>
@@ -1831,7 +1797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>70</v>
       </c>
@@ -1924,17 +1890,17 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-    </row>
-    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>74</v>
       </c>
@@ -1957,7 +1923,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>72</v>
       </c>
@@ -2005,7 +1971,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2028,7 +1994,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2044,10 +2010,10 @@
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -2059,18 +2025,18 @@
         <v>119</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
@@ -2082,18 +2048,18 @@
         <v>108</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>7</v>
@@ -2105,18 +2071,18 @@
         <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>7</v>
@@ -2128,18 +2094,18 @@
         <v>119</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>7</v>
@@ -2151,10 +2117,10 @@
         <v>119</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2170,10 +2136,10 @@
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>93</v>
@@ -2185,10 +2151,10 @@
         <v>119</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2204,7 +2170,7 @@
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>56</v>
@@ -2213,16 +2179,16 @@
         <v>93</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="20">
         <v>284</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,10 +2252,10 @@
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
@@ -2301,18 +2267,18 @@
         <v>102</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
@@ -2324,18 +2290,18 @@
         <v>102</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>7</v>
@@ -2347,56 +2313,56 @@
         <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="9">
         <v>406</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="26">
         <v>406</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2412,48 +2378,48 @@
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E10" s="14">
         <v>490</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E11" s="16">
         <v>492</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2469,79 +2435,79 @@
     </row>
     <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E13" s="4">
         <v>206</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14" s="4">
         <v>193</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15" s="4">
         <v>491</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>93</v>
@@ -2553,10 +2519,10 @@
         <v>102</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2570,27 +2536,27 @@
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="41" t="s">
+      <c r="B18" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="20">
+        <v>309</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="41">
-        <v>356</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>104</v>
+      <c r="G18" s="21" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям RU" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="141">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t xml:space="preserve">Валовая добавленная стоимость по регионам </t>
+  </si>
+  <si>
+    <t>Innovcosts_s.kz</t>
   </si>
 </sst>
 </file>
@@ -1957,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
@@ -2157,37 +2160,60 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="4">
+        <v>87</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B14" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C14" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E14" s="20">
         <v>284</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F14" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G14" s="21" t="s">
         <v>137</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="143">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -458,6 +458,12 @@
   </si>
   <si>
     <t>Innovcosts_s.kz</t>
+  </si>
+  <si>
+    <t>2022-2025</t>
+  </si>
+  <si>
+    <t>RDcosts_s.kz</t>
   </si>
 </sst>
 </file>
@@ -2160,6 +2166,29 @@
         <v>104</v>
       </c>
     </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="4">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>140</v>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="145">
   <si>
     <t xml:space="preserve">Название признака </t>
   </si>
@@ -464,6 +464,12 @@
   </si>
   <si>
     <t>RDcosts_s.kz</t>
+  </si>
+  <si>
+    <t>trainingcosts_s.kz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бюро национальной статистики Казахстана (информационно-коммуникационные технологии) </t>
   </si>
 </sst>
 </file>
@@ -1966,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
@@ -2168,42 +2174,42 @@
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="E11" s="4">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>133</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="E12" s="4">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>133</v>
@@ -2212,37 +2218,60 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="4">
+        <v>87</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B15" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C15" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D15" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E15" s="20">
         <v>284</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F15" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G15" s="21" t="s">
         <v>137</v>
       </c>
     </row>

--- a/description of features.xlsx
+++ b/description of features.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="По отраслям RU" sheetId="1" r:id="rId1"/>
@@ -632,9 +632,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -723,6 +720,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1007,7 +1005,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
+    <col min="2" max="2" width="44.5703125" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" customWidth="1"/>
@@ -1044,221 +1042,221 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="25">
         <v>11300</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="25">
         <v>6382</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="25">
         <v>6600</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="25">
         <v>11243</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>11251</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>2135</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <v>1345</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <v>1391</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -1329,7 +1327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>27</v>
       </c>
@@ -1422,59 +1420,59 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
     </row>
     <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>1207</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>570</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="20" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1490,7 +1488,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="48.85546875" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
@@ -1527,223 +1525,223 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="25">
         <v>846</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="25">
         <v>470</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="25">
         <v>470</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="25">
         <v>846</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>846</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>752</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="26" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <v>742</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <v>924</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+    </row>
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>67</v>
       </c>
@@ -1766,7 +1764,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>68</v>
       </c>
@@ -1789,7 +1787,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>69</v>
       </c>
@@ -1812,7 +1810,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>70</v>
       </c>
@@ -1835,7 +1833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>80</v>
       </c>
@@ -1905,59 +1903,59 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>846</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>846</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="20" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2013,133 +2011,133 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>119</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>108</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>2025</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="25">
         <v>21</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="25">
         <v>119</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="25" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>119</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B9" s="3"/>
@@ -2153,7 +2151,7 @@
       <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -2168,7 +2166,7 @@
       <c r="F10" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="29" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2176,7 +2174,7 @@
       <c r="A11" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>109</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -2199,7 +2197,7 @@
       <c r="A12" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>113</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2222,7 +2220,7 @@
       <c r="A13" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2242,36 +2240,36 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>284</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="20" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2324,190 +2322,190 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>102</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>102</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>2025</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>21</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>406</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="25" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>406</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>490</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="21" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>492</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="3"/>
@@ -2521,7 +2519,7 @@
       <c r="A13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="24" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2544,7 +2542,7 @@
       <c r="A14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>109</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2567,7 +2565,7 @@
       <c r="A15" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>113</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -2590,7 +2588,7 @@
       <c r="A16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2610,36 +2608,36 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="19">
         <v>309</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="20" t="s">
         <v>137</v>
       </c>
     </row>
